--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="484">
   <si>
     <t>Filename</t>
   </si>
@@ -811,658 +811,661 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9965,0.0006,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.0066,0.0001,0.0000,0.9983</t>
-  </si>
-  <si>
-    <t>0.9924,0.0005,0.0004,0.0036</t>
-  </si>
-  <si>
-    <t>0.0258,0.0010,0.0180,0.9675</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9764,0.0064,0.0027,0.0031</t>
+  </si>
+  <si>
+    <t>0.0025,0.0000,0.0000,0.9994</t>
+  </si>
+  <si>
+    <t>0.9820,0.0016,0.0035,0.0055</t>
+  </si>
+  <si>
+    <t>0.0097,0.0003,0.0003,0.9966</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9990,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
     <t>0.9998,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9994,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0920,0.0011,0.9167,0.0002</t>
-  </si>
-  <si>
-    <t>0.9018,0.0004,0.1468,0.0000</t>
-  </si>
-  <si>
-    <t>0.0107,0.0002,0.9886,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0000,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.9990,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0042,0.9951,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.2674,0.0007,0.7920,0.0002</t>
-  </si>
-  <si>
-    <t>0.9843,0.0001,0.0221,0.0001</t>
-  </si>
-  <si>
-    <t>0.0105,0.0001,0.9930,0.0000</t>
-  </si>
-  <si>
-    <t>0.0541,0.0101,0.9188,0.0007</t>
-  </si>
-  <si>
-    <t>0.0546,0.0001,0.9702,0.0000</t>
-  </si>
-  <si>
-    <t>0.0032,0.0000,0.9964,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0005</t>
-  </si>
-  <si>
-    <t>0.1404,0.9061,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.8874,0.0843,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.0026,0.9997,0.0640</t>
-  </si>
-  <si>
-    <t>0.0035,0.9354,0.1224,0.0001</t>
-  </si>
-  <si>
-    <t>0.9944,0.0015,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.0489,0.0009,0.9505,0.0022</t>
-  </si>
-  <si>
-    <t>0.9224,0.0872,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.1703,0.8204,0.0050,0.0002</t>
-  </si>
-  <si>
-    <t>0.0245,0.0103,0.9042,0.0028</t>
-  </si>
-  <si>
-    <t>0.0060,0.0169,0.9870,0.0037</t>
-  </si>
-  <si>
-    <t>0.0687,0.0085,0.9032,0.0005</t>
-  </si>
-  <si>
-    <t>0.0305,0.0000,0.9712,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.0036,0.9968,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9992,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0003,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9698,0.0009,0.8689</t>
-  </si>
-  <si>
-    <t>0.0003,0.9990,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.0041,0.9968,0.0001</t>
-  </si>
-  <si>
-    <t>0.0048,0.0000,0.9949,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9990,0.0003</t>
-  </si>
-  <si>
-    <t>0.9986,0.0013,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0013,0.9998,0.0047</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0001</t>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9508,0.0007,0.0553,0.0002</t>
+  </si>
+  <si>
+    <t>0.0206,0.0000,0.9849,0.0001</t>
+  </si>
+  <si>
+    <t>0.4638,0.0016,0.6185,0.0001</t>
+  </si>
+  <si>
+    <t>0.0053,0.0009,0.9902,0.0006</t>
+  </si>
+  <si>
+    <t>0.9947,0.0001,0.0064,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9982,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.9966,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9580,0.0001,0.0601,0.0003</t>
+  </si>
+  <si>
+    <t>0.9897,0.0000,0.0100,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0487,0.0007,0.9543,0.0004</t>
+  </si>
+  <si>
+    <t>0.0958,0.0001,0.9537,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0001,0.9971,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9997,0.0009</t>
+  </si>
+  <si>
+    <t>0.0914,0.9344,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9240,0.0514,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.0014,0.9998,0.0421</t>
+  </si>
+  <si>
+    <t>0.0109,0.9710,0.0108,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0400,0.0043,0.9440,0.0051</t>
+  </si>
+  <si>
+    <t>0.8934,0.1420,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.0128,0.9856,0.0048,0.0000</t>
+  </si>
+  <si>
+    <t>0.0212,0.0042,0.9438,0.0019</t>
+  </si>
+  <si>
+    <t>0.0763,0.0007,0.9299,0.0015</t>
+  </si>
+  <si>
+    <t>0.0380,0.0434,0.8880,0.0009</t>
+  </si>
+  <si>
+    <t>0.0114,0.0000,0.9887,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0015,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9970,0.0058,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.0005,0.9966,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.9800,0.0010,0.5194</t>
+  </si>
+  <si>
+    <t>0.0005,0.9978,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0158,0.9968,0.0001</t>
+  </si>
+  <si>
+    <t>0.1760,0.0000,0.9210,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0000,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.1572,0.9917,0.0005</t>
+  </si>
+  <si>
+    <t>0.9989,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9996,0.0089</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9994,0.0003,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.9951,0.3830,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.0004,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9927,0.9971,0.0000</t>
+    <t>0.0000,0.9954,0.9028,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0021,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0019,0.0002,0.9946,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.9911,0.9946,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0025,0.9963,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9873,0.0006,0.0094,0.0002</t>
-  </si>
-  <si>
-    <t>0.9343,0.0046,0.0367,0.0019</t>
-  </si>
-  <si>
-    <t>0.0002,0.0033,0.9997,0.0020</t>
-  </si>
-  <si>
-    <t>0.0000,0.9955,0.9958,0.0000</t>
-  </si>
-  <si>
-    <t>0.0088,0.3268,0.8799,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0846,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9948,0.9634,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0000,0.0079,0.9971</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.0032,0.9990</t>
-  </si>
-  <si>
-    <t>0.0028,0.0002,0.0045,0.9960</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9928,0.8887,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.8959,0.9976,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.5158,0.9656,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.7791,0.9443,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9973,0.9628,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9192,0.9559,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
+    <t>0.0011,0.9983,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9737,0.0003,0.0290,0.0001</t>
+  </si>
+  <si>
+    <t>0.9727,0.0027,0.0098,0.0020</t>
+  </si>
+  <si>
+    <t>0.0057,0.0006,0.9928,0.0030</t>
+  </si>
+  <si>
+    <t>0.0012,0.8645,0.8522,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9828,0.9744,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0040,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9977,0.9627,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.0000,0.0389,0.9882</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0017,0.0001,0.0011,0.9984</t>
+  </si>
+  <si>
+    <t>0.0017,0.0003,0.0038,0.9969</t>
+  </si>
+  <si>
+    <t>0.0001,0.9915,0.9335,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9538,0.9908,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9877,0.9187,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9222,0.9776,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.3235,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.8102,0.8813,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0021,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0001,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.9985,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0084,0.9874,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.0066,0.9904,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9282,0.0848,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9190,0.0314,0.0081,0.0007</t>
+  </si>
+  <si>
+    <t>0.6871,0.0002,0.4174,0.0002</t>
+  </si>
+  <si>
+    <t>0.9318,0.0057,0.0349,0.0005</t>
+  </si>
+  <si>
+    <t>0.7915,0.0008,0.2579,0.0005</t>
+  </si>
+  <si>
+    <t>0.0008,0.0003,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9982,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.9509,0.0000</t>
+  </si>
+  <si>
+    <t>0.0958,0.9413,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.9739,0.0322,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9863,0.0210,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.7594,0.8817,0.0011</t>
+  </si>
+  <si>
+    <t>0.0240,0.0861,0.8523,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.0013,0.9959,0.0001</t>
+  </si>
+  <si>
+    <t>0.0197,0.0017,0.9733,0.0004</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9522,0.0016,0.0221,0.0018</t>
+  </si>
+  <si>
+    <t>0.2320,0.0000,0.8443,0.0002</t>
+  </si>
+  <si>
+    <t>0.9967,0.0001,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0155,0.0001,0.0001,0.9948</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.9138,0.9893,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.9933,0.0021,0.0028</t>
+  </si>
+  <si>
+    <t>0.0442,0.9511,0.0049,0.0003</t>
+  </si>
+  <si>
+    <t>0.9977,0.0001,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.7305,0.0001,0.0114,0.1818</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0089,0.9977,0.0334</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9944,0.0004,0.0010,0.0014</t>
+  </si>
+  <si>
+    <t>0.0789,0.9140,0.0035,0.0004</t>
+  </si>
+  <si>
+    <t>0.9966,0.0024,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9920,0.0074,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.4415,0.2466,0.0284,0.0007</t>
+  </si>
+  <si>
+    <t>0.9943,0.0067,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0020,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.8255,0.1203,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.3813,0.7353,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.4018,0.7862,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9803,0.0047,0.0073,0.0003</t>
+  </si>
+  <si>
+    <t>0.9752,0.0308,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9890,0.0080,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9565,0.0535,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0013,1.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9932,0.0013,0.0025,0.0008</t>
+  </si>
+  <si>
+    <t>0.0046,0.0213,0.9864,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0035,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.5878,0.0012,0.4905,0.0001</t>
+  </si>
+  <si>
+    <t>0.0106,0.0009,0.9878,0.0003</t>
+  </si>
+  <si>
+    <t>0.0062,0.0008,0.9901,0.0005</t>
+  </si>
+  <si>
+    <t>0.3584,0.0434,0.3346,0.0006</t>
+  </si>
+  <si>
+    <t>0.0015,0.4080,0.9062,0.0010</t>
+  </si>
+  <si>
+    <t>0.2550,0.0014,0.8056,0.0002</t>
+  </si>
+  <si>
+    <t>0.9813,0.0009,0.0090,0.0007</t>
+  </si>
+  <si>
+    <t>0.6604,0.0010,0.3681,0.0010</t>
+  </si>
+  <si>
+    <t>0.0052,0.9921,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.0252,0.9829,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9759,0.0437,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9927,0.0110,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0395,0.9724,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9713,0.0049,0.0076,0.0002</t>
+  </si>
+  <si>
+    <t>0.9968,0.0001,0.0020,0.0000</t>
+  </si>
+  <si>
+    <t>0.9898,0.0011,0.0021,0.0003</t>
+  </si>
+  <si>
+    <t>0.9635,0.0009,0.0330,0.0003</t>
+  </si>
+  <si>
+    <t>0.9279,0.0003,0.0982,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.0010,0.9975,0.0026</t>
+  </si>
+  <si>
+    <t>0.0183,0.1397,0.6689,0.0047</t>
+  </si>
+  <si>
+    <t>0.0298,0.0068,0.9646,0.0002</t>
+  </si>
+  <si>
+    <t>0.0868,0.0030,0.9221,0.0005</t>
+  </si>
+  <si>
+    <t>0.0183,0.0081,0.9651,0.0011</t>
+  </si>
+  <si>
+    <t>0.9987,0.0011,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0023,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9995,0.0006,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9996,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0018,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0047,0.9988,0.0003</t>
-  </si>
-  <si>
-    <t>0.9984,0.0000,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.9985,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0089,0.9878,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.0047,0.9935,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8783,0.1509,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.6630,0.0053,0.2185,0.0018</t>
-  </si>
-  <si>
-    <t>0.9850,0.0001,0.0173,0.0001</t>
-  </si>
-  <si>
-    <t>0.9865,0.0014,0.0032,0.0003</t>
-  </si>
-  <si>
-    <t>0.9108,0.0019,0.0891,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0091,0.0000,0.9991</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9972,0.9274,0.0000</t>
-  </si>
-  <si>
-    <t>0.0105,0.9907,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.9676,0.0505,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9689,0.0321,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0010,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.1712,0.9918,0.0004</t>
-  </si>
-  <si>
-    <t>0.0111,0.0610,0.9380,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0014,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9930,0.0005,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.0201,0.0000,0.9831,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.2443,0.0001,0.0001,0.9086</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0003,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.9902,0.9913,0.0000</t>
-  </si>
-  <si>
-    <t>0.0559,0.9376,0.0036,0.0015</t>
-  </si>
-  <si>
-    <t>0.0264,0.9565,0.0107,0.0005</t>
-  </si>
-  <si>
-    <t>0.0379,0.0005,0.0051,0.9678</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0161,0.9964,0.0151</t>
-  </si>
-  <si>
-    <t>0.9967,0.0001,0.0013,0.0012</t>
-  </si>
-  <si>
-    <t>0.9850,0.0006,0.0043,0.0011</t>
-  </si>
-  <si>
-    <t>0.3181,0.7273,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9954,0.0040,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9477,0.0144,0.0111,0.0004</t>
-  </si>
-  <si>
-    <t>0.9843,0.0082,0.0028,0.0002</t>
-  </si>
-  <si>
-    <t>0.9979,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9950,0.0045,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9772,0.0077,0.0002,0.0015</t>
-  </si>
-  <si>
-    <t>0.9492,0.0975,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9030,0.1721,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9809,0.0080,0.0052,0.0004</t>
-  </si>
-  <si>
-    <t>0.9888,0.0084,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9980,0.0008,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0019,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9755,0.0355,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0018,0.9999,0.0005</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.0032,0.9959,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.0000,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0093,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0003,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9990,0.0022</t>
-  </si>
-  <si>
-    <t>0.0077,0.0010,0.9899,0.0001</t>
-  </si>
-  <si>
-    <t>0.0409,0.0094,0.9488,0.0005</t>
-  </si>
-  <si>
-    <t>0.4015,0.0313,0.3191,0.0011</t>
-  </si>
-  <si>
-    <t>0.0459,0.0040,0.9454,0.0004</t>
-  </si>
-  <si>
-    <t>0.0316,0.3066,0.5233,0.0008</t>
-  </si>
-  <si>
-    <t>0.0062,0.0034,0.9914,0.0005</t>
-  </si>
-  <si>
-    <t>0.5248,0.0040,0.3916,0.0027</t>
-  </si>
-  <si>
-    <t>0.4990,0.0045,0.4848,0.0007</t>
-  </si>
-  <si>
-    <t>0.0101,0.9909,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.9968,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.8015,0.2904,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9733,0.0403,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.3584,0.7780,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9135,0.0354,0.0112,0.0002</t>
-  </si>
-  <si>
-    <t>0.9950,0.0001,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.9343,0.0038,0.0314,0.0041</t>
-  </si>
-  <si>
-    <t>0.9624,0.0006,0.0399,0.0002</t>
-  </si>
-  <si>
-    <t>0.9116,0.0001,0.1353,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9993,0.0004</t>
-  </si>
-  <si>
-    <t>0.1115,0.0020,0.8484,0.0022</t>
-  </si>
-  <si>
-    <t>0.0120,0.0049,0.9842,0.0001</t>
-  </si>
-  <si>
-    <t>0.3281,0.0001,0.7791,0.0001</t>
-  </si>
-  <si>
-    <t>0.0195,0.0012,0.9754,0.0004</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0022,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0003,0.9987,0.0007</t>
-  </si>
-  <si>
-    <t>0.3716,0.0868,0.1886,0.0014</t>
-  </si>
-  <si>
-    <t>0.9933,0.0015,0.0009,0.0013</t>
-  </si>
-  <si>
-    <t>0.0059,0.0001,0.9959,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9998,0.0005</t>
-  </si>
-  <si>
-    <t>0.0007,0.1007,0.9614,0.0058</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0004,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0054,0.0046,0.9872,0.0014</t>
-  </si>
-  <si>
-    <t>0.9892,0.0000,0.0172,0.0001</t>
-  </si>
-  <si>
-    <t>0.9860,0.0001,0.0177,0.0000</t>
-  </si>
-  <si>
-    <t>0.9958,0.0001,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0012,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0031,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0017,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0033,0.0007,0.9955,0.0001</t>
-  </si>
-  <si>
-    <t>0.0055,0.0060,0.9855,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.9446,0.0000,0.0903,0.0002</t>
-  </si>
-  <si>
-    <t>0.0134,0.0005,0.9851,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9984,0.0006</t>
-  </si>
-  <si>
-    <t>0.9955,0.0000,0.0010,0.0026</t>
-  </si>
-  <si>
-    <t>0.1434,0.0004,0.0000,0.9443</t>
-  </si>
-  <si>
-    <t>0.0016,0.0000,0.0029,0.9976</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9964,0.0001,0.0003,0.0015</t>
+    <t>0.9989,0.0007,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0011,0.9992,0.0010</t>
+  </si>
+  <si>
+    <t>0.3114,0.5767,0.0173,0.0015</t>
+  </si>
+  <si>
+    <t>0.5771,0.0016,0.2950,0.0173</t>
+  </si>
+  <si>
+    <t>0.0013,0.0003,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.0265,0.9846,0.0014</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.0006,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0049,0.0149,0.9862,0.0016</t>
+  </si>
+  <si>
+    <t>0.9418,0.0005,0.0607,0.0012</t>
+  </si>
+  <si>
+    <t>0.9743,0.0001,0.0455,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0001,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.9963,0.0052,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9949,0.0059,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0015,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0048,0.9969,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0048,0.0018,0.9908,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.4341,0.0000,0.6624,0.0003</t>
+  </si>
+  <si>
+    <t>0.0041,0.0002,0.9945,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9977,0.0011</t>
+  </si>
+  <si>
+    <t>0.9977,0.0000,0.0003,0.0020</t>
+  </si>
+  <si>
+    <t>0.2060,0.0000,0.0000,0.9683</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.0033,0.9985</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9835,0.0005,0.0007,0.0076</t>
   </si>
 </sst>
 </file>
@@ -1848,7 +1851,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1862,7 +1865,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1876,7 +1879,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1890,7 +1893,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1904,7 +1907,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1918,7 +1921,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1932,7 +1935,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1946,7 +1949,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1960,7 +1963,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1974,7 +1977,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1988,7 +1991,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2002,7 +2005,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2016,7 +2019,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2030,7 +2033,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2041,10 +2044,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2058,7 +2061,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2072,7 +2075,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2086,7 +2089,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2100,7 +2103,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2114,7 +2117,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2128,7 +2131,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2142,7 +2145,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2153,10 +2156,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2170,7 +2173,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2184,7 +2187,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2198,7 +2201,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2212,7 +2215,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2226,7 +2229,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2240,7 +2243,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2254,7 +2257,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2268,7 +2271,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2282,7 +2285,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2296,7 +2299,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2310,7 +2313,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2324,7 +2327,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2338,7 +2341,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2352,7 +2355,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2366,7 +2369,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2380,7 +2383,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2394,7 +2397,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2408,7 +2411,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2422,7 +2425,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2436,7 +2439,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2450,7 +2453,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2464,7 +2467,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2478,7 +2481,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2492,7 +2495,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2506,7 +2509,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2520,7 +2523,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2534,7 +2537,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2548,7 +2551,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2562,7 +2565,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2576,7 +2579,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2590,7 +2593,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2604,7 +2607,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2618,7 +2621,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>270</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2632,7 +2635,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2646,7 +2649,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2660,7 +2663,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2674,7 +2677,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>269</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2688,7 +2691,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2699,10 +2702,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2716,7 +2719,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2730,7 +2733,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2744,7 +2747,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2758,7 +2761,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2772,7 +2775,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2786,7 +2789,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2800,7 +2803,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2814,7 +2817,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2828,7 +2831,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2842,7 +2845,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2853,10 +2856,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2870,7 +2873,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2884,7 +2887,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2898,7 +2901,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2912,7 +2915,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2926,7 +2929,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2940,7 +2943,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2954,7 +2957,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2968,7 +2971,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2982,7 +2985,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2996,7 +2999,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3010,7 +3013,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3024,7 +3027,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3035,10 +3038,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3052,7 +3055,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3066,7 +3069,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>347</v>
+        <v>273</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3080,7 +3083,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3094,7 +3097,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3108,7 +3111,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3122,7 +3125,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3150,7 +3153,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3164,7 +3167,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>269</v>
+        <v>353</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3178,7 +3181,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3192,7 +3195,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3206,7 +3209,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3220,7 +3223,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3248,7 +3251,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3262,7 +3265,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3276,7 +3279,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3290,7 +3293,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3304,7 +3307,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3318,7 +3321,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3332,7 +3335,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3346,7 +3349,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3360,7 +3363,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3374,7 +3377,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3388,7 +3391,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3402,7 +3405,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3416,7 +3419,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3430,7 +3433,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3444,7 +3447,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3458,7 +3461,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3472,7 +3475,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3486,7 +3489,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3500,7 +3503,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3514,7 +3517,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3528,7 +3531,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>371</v>
+        <v>330</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3542,7 +3545,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3556,7 +3559,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3570,7 +3573,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3584,7 +3587,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3598,7 +3601,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3612,7 +3615,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3626,7 +3629,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3640,7 +3643,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>271</v>
+        <v>378</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3654,7 +3657,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3668,7 +3671,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>271</v>
+        <v>355</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3682,7 +3685,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3696,7 +3699,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>378</v>
+        <v>271</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3710,7 +3713,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>271</v>
+        <v>380</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3721,10 +3724,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3738,7 +3741,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3752,7 +3755,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3766,7 +3769,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3780,7 +3783,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3794,7 +3797,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3808,7 +3811,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3822,7 +3825,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3836,7 +3839,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3850,7 +3853,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3864,7 +3867,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>340</v>
+        <v>390</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3878,7 +3881,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3892,7 +3895,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3906,7 +3909,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>269</v>
+        <v>378</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3920,7 +3923,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3934,7 +3937,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3948,7 +3951,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3962,7 +3965,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3973,10 +3976,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3990,7 +3993,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4004,7 +4007,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4018,7 +4021,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4032,7 +4035,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4046,7 +4049,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4060,7 +4063,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4074,7 +4077,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4085,10 +4088,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D162" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4102,7 +4105,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4116,7 +4119,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4130,7 +4133,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>271</v>
+        <v>407</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4144,7 +4147,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>271</v>
+        <v>408</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4158,7 +4161,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4172,7 +4175,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>404</v>
+        <v>273</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4186,7 +4189,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4200,7 +4203,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4228,7 +4231,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4242,7 +4245,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4253,10 +4256,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4267,10 +4270,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4284,7 +4287,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4298,7 +4301,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4312,7 +4315,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4326,7 +4329,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4340,7 +4343,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4354,7 +4357,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4368,7 +4371,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4382,7 +4385,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>416</v>
+        <v>288</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4396,7 +4399,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4410,7 +4413,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4424,7 +4427,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4438,7 +4441,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4452,7 +4455,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4466,7 +4469,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4477,10 +4480,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D190" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4494,7 +4497,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4505,10 +4508,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4519,10 +4522,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D193" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4536,7 +4539,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4550,7 +4553,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4564,7 +4567,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4578,7 +4581,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4592,7 +4595,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4606,7 +4609,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4620,7 +4623,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4634,7 +4637,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4648,7 +4651,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4662,7 +4665,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4676,7 +4679,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4690,7 +4693,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4704,7 +4707,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4718,7 +4721,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4732,7 +4735,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4746,7 +4749,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4760,7 +4763,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4774,7 +4777,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4788,7 +4791,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4802,7 +4805,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>445</v>
+        <v>353</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4816,7 +4819,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4830,7 +4833,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4844,7 +4847,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>349</v>
+        <v>451</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4858,7 +4861,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4872,7 +4875,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>449</v>
+        <v>349</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4886,7 +4889,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>450</v>
+        <v>270</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4900,7 +4903,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4914,7 +4917,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4925,10 +4928,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4942,7 +4945,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4956,7 +4959,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4970,7 +4973,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4984,7 +4987,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4998,7 +5001,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5012,7 +5015,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5026,7 +5029,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5040,7 +5043,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5054,7 +5057,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5068,7 +5071,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5082,7 +5085,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5096,7 +5099,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5110,7 +5113,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>465</v>
+        <v>408</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5124,7 +5127,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>271</v>
+        <v>467</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5138,7 +5141,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>348</v>
+        <v>275</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5152,7 +5155,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5166,7 +5169,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5180,7 +5183,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>467</v>
+        <v>351</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5194,7 +5197,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5208,7 +5211,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>468</v>
+        <v>270</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5222,7 +5225,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5236,7 +5239,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5250,7 +5253,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5264,7 +5267,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5278,7 +5281,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5289,10 +5292,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5306,7 +5309,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5320,7 +5323,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5334,7 +5337,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5348,7 +5351,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5362,7 +5365,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5376,7 +5379,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5390,7 +5393,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5404,7 +5407,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
